--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126727655</v>
+        <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479592</v>
+        <v>479615</v>
       </c>
       <c r="R2" t="n">
-        <v>6858868</v>
+        <v>6858888</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +774,74 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727655</t>
+          <t>https://artportalen.se/Sighting/136127285</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126727658</v>
+        <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>93357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479672</v>
+        <v>479652</v>
       </c>
       <c r="R3" t="n">
-        <v>6858565</v>
+        <v>6858751</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,62 +885,71 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727658</t>
+          <t>https://artportalen.se/Sighting/136127662</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126727661</v>
+        <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>93357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479700</v>
+        <v>479854</v>
       </c>
       <c r="R4" t="n">
-        <v>6858487</v>
+        <v>6858612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +996,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727661</t>
+          <t>https://artportalen.se/Sighting/136129359</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126727663</v>
+        <v>126727655</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479687</v>
+        <v>479592</v>
       </c>
       <c r="R5" t="n">
-        <v>6858473</v>
+        <v>6858868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,21 +1095,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1097,16 +1109,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727663</t>
+          <t>https://artportalen.se/Sighting/126727655</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126727656</v>
+        <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>93363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1126,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479591</v>
+        <v>479611</v>
       </c>
       <c r="R6" t="n">
-        <v>6858845</v>
+        <v>6858862</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,27 +1209,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727656</t>
+          <t>https://artportalen.se/Sighting/136127498</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126727657</v>
+        <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1237,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479638</v>
+        <v>479669</v>
       </c>
       <c r="R7" t="n">
-        <v>6858782</v>
+        <v>6858726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,12 +1291,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,27 +1311,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727657</t>
+          <t>https://artportalen.se/Sighting/136127726</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126727648</v>
+        <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,37 +1339,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479845</v>
+        <v>479661</v>
       </c>
       <c r="R8" t="n">
-        <v>6858567</v>
+        <v>6858644</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1372,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,46 +1418,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727648</t>
+          <t>https://artportalen.se/Sighting/136127866</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126727651</v>
+        <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>79085</v>
+        <v>93363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,37 +1450,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479864</v>
+        <v>479657</v>
       </c>
       <c r="R9" t="n">
-        <v>6858579</v>
+        <v>6858560</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1489,12 +1513,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,46 +1529,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727651</t>
+          <t>https://artportalen.se/Sighting/136127969</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126727653</v>
+        <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>79085</v>
+        <v>93363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,37 +1561,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479609</v>
+        <v>479677</v>
       </c>
       <c r="R10" t="n">
-        <v>6858855</v>
+        <v>6858465</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,12 +1624,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,46 +1640,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727653</t>
+          <t>https://artportalen.se/Sighting/136129097</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126727664</v>
+        <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>79085</v>
+        <v>93363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,37 +1672,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479688</v>
+        <v>479719</v>
       </c>
       <c r="R11" t="n">
-        <v>6858472</v>
+        <v>6858554</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,12 +1735,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,46 +1751,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727664</t>
+          <t>https://artportalen.se/Sighting/136129146</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126727649</v>
+        <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>79917</v>
+        <v>93363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,37 +1783,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479845</v>
+        <v>479831</v>
       </c>
       <c r="R12" t="n">
-        <v>6858567</v>
+        <v>6858563</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1840,12 +1851,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,46 +1872,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727649</t>
+          <t>https://artportalen.se/Sighting/136129217</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126727659</v>
+        <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>79917</v>
+        <v>93363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,34 +1904,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479748</v>
+        <v>479838</v>
       </c>
       <c r="R13" t="n">
-        <v>6858531</v>
+        <v>6858616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,12 +1967,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,46 +1983,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126727659</t>
+          <t>https://artportalen.se/Sighting/136129313</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126727662</v>
+        <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>79917</v>
+        <v>93363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,34 +2015,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479689</v>
+        <v>479813</v>
       </c>
       <c r="R14" t="n">
-        <v>6858474</v>
+        <v>6858608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,12 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,35 +2094,2429 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136129466</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136129503</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93363</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>479815</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6858627</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136129503</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136129379</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93375</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>479854</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6858612</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136129379</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126727658</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>479672</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6858565</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727658</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126727661</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>479700</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6858487</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727661</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136127218</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79444</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>479575</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6858912</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136127218</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126727663</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>479687</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6858473</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727663</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126727656</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>479591</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6858845</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727656</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126727657</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>479638</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6858782</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727657</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136127205</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>479568</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6858917</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136127205</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136127467</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>479623</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6858930</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136127467</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136128577</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>479607</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6858463</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136128577</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136128639</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rötaåsen, Rötaåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>479651</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6858469</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136128639</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136128691</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>479677</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6858465</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136128691</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136129544</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>479816</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6858631</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136129544</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136129558</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Stortjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>479799</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6858639</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136129558</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126727648</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>479845</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6858567</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727648</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126727651</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>479864</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6858579</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727651</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126727653</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>479609</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6858855</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727653</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126727664</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>479688</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6858472</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727664</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126727649</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>479845</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6858567</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727649</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126727659</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>479748</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6858531</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126727659</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126727662</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>479689</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6858474</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126727662</t>
         </is>
@@ -2139,6 +4537,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93376</v>
+        <v>93377</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93384</v>
+        <v>93390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93390</v>
+        <v>93397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
